--- a/AAII_Financials/Quarterly/TBNGY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TBNGY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="424" uniqueCount="92">
   <si>
     <t>TBNGY</t>
   </si>
@@ -656,87 +656,91 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -785,8 +789,11 @@
       <c r="R8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -835,8 +842,11 @@
       <c r="R9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -885,8 +895,11 @@
       <c r="R10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -905,8 +918,9 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -955,8 +969,11 @@
       <c r="R12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1005,8 +1022,11 @@
       <c r="R13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1055,8 +1075,11 @@
       <c r="R14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1105,8 +1128,11 @@
       <c r="R15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1122,8 +1148,9 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1172,8 +1199,11 @@
       <c r="R17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1222,8 +1252,11 @@
       <c r="R18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1242,8 +1275,9 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1292,8 +1326,11 @@
       <c r="R20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1342,8 +1379,11 @@
       <c r="R21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1392,8 +1432,11 @@
       <c r="R22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1442,8 +1485,11 @@
       <c r="R23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1492,8 +1538,11 @@
       <c r="R24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1542,8 +1591,11 @@
       <c r="R25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1592,8 +1644,11 @@
       <c r="R26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1642,8 +1697,11 @@
       <c r="R27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1692,8 +1750,11 @@
       <c r="R28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1742,8 +1803,11 @@
       <c r="R29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1792,8 +1856,11 @@
       <c r="R30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1842,8 +1909,11 @@
       <c r="R31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1892,8 +1962,11 @@
       <c r="R32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1942,8 +2015,11 @@
       <c r="R33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1992,8 +2068,11 @@
       <c r="R34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -2042,63 +2121,69 @@
       <c r="R35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2117,8 +2202,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2137,458 +2223,486 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>384400</v>
+      </c>
+      <c r="E41" s="3">
         <v>247300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>270700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>240000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>248800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>294100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>256700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>299800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>277200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>234400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>268500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>343700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1053700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>389400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>452700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>349200</v>
       </c>
     </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>23800</v>
+      </c>
+      <c r="E42" s="3">
         <v>26500</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>28100</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>27100</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>26600</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>25800</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>41500</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>30600</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>28400</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>61400</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>91900</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>96100</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>128600</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>699600</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>625400</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>605200</v>
       </c>
     </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>275500</v>
+      </c>
+      <c r="E43" s="3">
         <v>291400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>239700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>323800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>354300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>270400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>321700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>293400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>258800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>303500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>254900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>181400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>226500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>305300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>226000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>281500</v>
       </c>
     </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>234000</v>
+      </c>
+      <c r="E44" s="3">
         <v>199400</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>292300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>282000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>267900</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>260200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>302500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>315600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>245000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>261100</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>356800</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>267200</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>197700</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>205600</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>247100</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>181500</v>
       </c>
     </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E45" s="3">
         <v>2500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>3700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>46500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>77900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>7500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>13700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>34600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>26300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>21200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>10500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>20100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>20900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>24600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>22100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>19800</v>
       </c>
     </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>924100</v>
+      </c>
+      <c r="E46" s="3">
         <v>769600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>852600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>921500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>978000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>860800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>946300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>974000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>835700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>881500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>982800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>908600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1627400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1624500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1573300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1437200</v>
       </c>
     </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>598900</v>
+      </c>
+      <c r="E47" s="3">
         <v>577500</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>576000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>557000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>549900</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>529900</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>539300</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>538600</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>492300</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>494600</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>471200</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>444000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>455400</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>458000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>421400</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>395700</v>
       </c>
     </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>844100</v>
+      </c>
+      <c r="E48" s="3">
         <v>883900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>885600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>826900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>812100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>768400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>754600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>774100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>718500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>739700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>772700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>722100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>742700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>741000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>730000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>704300</v>
       </c>
     </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>5700</v>
+      </c>
+      <c r="E49" s="3">
         <v>6000</v>
-      </c>
-      <c r="E49" s="3">
-        <v>6100</v>
       </c>
       <c r="F49" s="3">
         <v>6100</v>
       </c>
       <c r="G49" s="3">
+        <v>6100</v>
+      </c>
+      <c r="H49" s="3">
         <v>6300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>6200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>6300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>6700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>6200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>6400</v>
-      </c>
-      <c r="M49" s="3">
-        <v>6600</v>
       </c>
       <c r="N49" s="3">
         <v>6600</v>
       </c>
       <c r="O49" s="3">
-        <v>6800</v>
+        <v>6600</v>
       </c>
       <c r="P49" s="3">
         <v>6800</v>
       </c>
       <c r="Q49" s="3">
+        <v>6800</v>
+      </c>
+      <c r="R49" s="3">
         <v>6600</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>6700</v>
       </c>
     </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2637,8 +2751,11 @@
       <c r="R50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2687,58 +2804,64 @@
       <c r="R51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>247600</v>
+      </c>
+      <c r="E52" s="3">
         <v>236600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>230700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>177800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>203100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>310900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>270900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>256700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>221000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>211500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>191000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>176800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>180100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>188500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>115500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>91300</v>
       </c>
     </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2787,58 +2910,64 @@
       <c r="R53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2688900</v>
+      </c>
+      <c r="E54" s="3">
         <v>2550100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2629100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2566500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2629300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2551900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2595700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2652100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2348300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2423300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>2514900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>2327200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>3083000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>3100200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>2920900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>2706600</v>
       </c>
     </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2857,8 +2986,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2877,308 +3007,327 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>172900</v>
+      </c>
+      <c r="E57" s="3">
         <v>122600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>217000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>241700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>269200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>194600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>181400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>230600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>156500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>146000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>135100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>161000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>143200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>177900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>124700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>142600</v>
       </c>
     </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>19400</v>
+      </c>
+      <c r="E58" s="3">
         <v>20600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>139200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>228200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>57700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>103300</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>117000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>161000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>182300</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>34000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>36200</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>31800</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>32500</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>39100</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>38100</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>21800</v>
       </c>
     </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>162000</v>
+      </c>
+      <c r="E59" s="3">
         <v>99600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>104000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>86000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>324300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>96500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>98400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>91600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>98700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>94800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>113100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>70800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>895200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>105400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>110600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>118600</v>
       </c>
     </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>766100</v>
+      </c>
+      <c r="E60" s="3">
         <v>607000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>761900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>899000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>965800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>724400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>743900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>834600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>724600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>559300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>646700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>657900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1416200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>709600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>689100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>640000</v>
       </c>
     </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>147500</v>
+      </c>
+      <c r="E61" s="3">
         <v>139800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>91800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>15500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>18000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>17800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>22900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>31600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>35900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>43100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>48200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>51300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>61400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>44500</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>49600</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>60200</v>
       </c>
     </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>117900</v>
+      </c>
+      <c r="E62" s="3">
         <v>128500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>129000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>102000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>109200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>105300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>108200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>107400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>104900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>107500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>116000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>100900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>102800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>102500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>98900</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>83800</v>
       </c>
     </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3227,8 +3376,11 @@
       <c r="R63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3277,8 +3429,11 @@
       <c r="R64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3327,58 +3482,64 @@
       <c r="R65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1272500</v>
+      </c>
+      <c r="E66" s="3">
         <v>1153800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1275200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1321900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1410400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1158700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1189100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1308800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1154100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1005200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1116000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1071500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1853000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1114600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1058900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>970700</v>
       </c>
     </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3397,8 +3558,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3447,8 +3609,11 @@
       <c r="R68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3497,8 +3662,11 @@
       <c r="R69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3547,8 +3715,11 @@
       <c r="R70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3597,58 +3768,64 @@
       <c r="R71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1190600</v>
+      </c>
+      <c r="E72" s="3">
         <v>1197500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>1153700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>1044900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>1030000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>1208100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>1217500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>1160800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>1014800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>1254700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>1233900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>1100700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>1071600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>1815900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>1693100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>1586800</v>
       </c>
     </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3697,8 +3874,11 @@
       <c r="R73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3747,8 +3927,11 @@
       <c r="R74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3797,58 +3980,64 @@
       <c r="R75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1410100</v>
+      </c>
+      <c r="E76" s="3">
         <v>1388300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1346000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1238000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1209900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1384500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1398000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1334600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1186600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1409200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1390600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1243300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1218300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1970000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1848500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1715700</v>
       </c>
     </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3897,63 +4086,69 @@
       <c r="R77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -4002,8 +4197,11 @@
       <c r="R81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4022,58 +4220,62 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>24600</v>
+      </c>
+      <c r="E83" s="3">
         <v>28500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>31700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>30400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>26300</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>25100</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>42200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>76400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>-24400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>24500</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>29000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>24000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>28900</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>19900</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>25200</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>22300</v>
       </c>
     </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4122,8 +4324,11 @@
       <c r="R84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4172,8 +4377,11 @@
       <c r="R85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4222,8 +4430,11 @@
       <c r="R86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4272,8 +4483,11 @@
       <c r="R87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4322,58 +4536,64 @@
       <c r="R88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>143400</v>
+      </c>
+      <c r="E89" s="3">
         <v>121500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>123200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>118600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>62300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>73200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>41400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>86900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>170800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>17300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-46800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>127300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>113500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>10200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>192200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>221500</v>
       </c>
     </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4392,58 +4612,62 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-12900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-54000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-63300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-55000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-56300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-37200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>10800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-29400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-26100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-33700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-27000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-17900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-4100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-12300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-31500</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-7200</v>
       </c>
     </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4492,8 +4716,11 @@
       <c r="R92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4542,58 +4769,64 @@
       <c r="R93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-11300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-62400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-71700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-52100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-56300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-25500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-7300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-29300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>12600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-37200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-20600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>9400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>575200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-80600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-63800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-138900</v>
       </c>
     </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4612,58 +4845,62 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E96" s="3">
-        <v>0</v>
+      <c r="E96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F96" s="3">
+        <v>0</v>
+      </c>
+      <c r="G96" s="3">
         <v>229300</v>
       </c>
-      <c r="G96" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K96" s="3">
+      <c r="I96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J96" s="3">
+        <v>0</v>
+      </c>
+      <c r="K96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L96" s="3">
         <v>280100</v>
       </c>
-      <c r="L96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N96" s="3">
+        <v>0</v>
+      </c>
+      <c r="O96" s="3">
         <v>812300</v>
       </c>
-      <c r="O96" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
-      </c>
-      <c r="R96" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+      <c r="S96" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4712,8 +4949,11 @@
       <c r="R97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4762,8 +5002,11 @@
       <c r="R98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4812,154 +5055,166 @@
       <c r="R99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>15800</v>
+      </c>
+      <c r="E100" s="3">
         <v>-79200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-20700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-70600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-54200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-7000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-65900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-43900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-137500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-10400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-7400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-819900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-21300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-8400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-20100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-7100</v>
       </c>
     </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E101" s="3">
         <v>3800</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>6500</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-13200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>4100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>3600</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-1700</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>4300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-1600</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-1800</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>2100</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>200</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>2400</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
-      </c>
       <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+      <c r="R101" s="3">
         <v>600</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-1200</v>
       </c>
     </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>150000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-19500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>30900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-2000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-51200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>44500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-25300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>49900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-26700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-76500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-678900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>665800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-80600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>110300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>75700</v>
       </c>
     </row>
